--- a/apps/shell/resources/templates/Budget Planner.xlsx
+++ b/apps/shell/resources/templates/Budget Planner.xlsx
@@ -1004,8 +1004,8 @@
   <pageMargins left="0.45" right="0.45" top="0.65" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;9 &amp;K667085&amp;BPLOT DOCS SUITE&amp;"Calibri,Bold"  /  Budget Planner</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K667085Built with Plot Docs Suite&amp;R&amp;8 &amp;K667085Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;C&amp;9 &amp;K667085&amp;BPLOT DOCS&amp;"Calibri,Bold"  /  Budget Planner</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K667085Built with Plot Docs&amp;R&amp;8 &amp;K667085Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1098,8 +1098,8 @@
   <pageMargins left="0.45" right="0.45" top="0.65" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;9 &amp;K667085&amp;BPLOT DOCS SUITE&amp;"Calibri,Bold"  /  Budget Planner · Guide</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K667085Built with Plot Docs Suite&amp;R&amp;8 &amp;K667085Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;C&amp;9 &amp;K667085&amp;BPLOT DOCS&amp;"Calibri,Bold"  /  Budget Planner · Guide</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K667085Built with Plot Docs&amp;R&amp;8 &amp;K667085Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
